--- a/output/details/2026-05-13/preprocessed_data.xlsx
+++ b/output/details/2026-05-13/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46155</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1083044754774606</v>
+        <v>-0.1081841539863215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1976129676155109</v>
+        <v>-0.1294621119754789</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1973284263596352</v>
+        <v>-0.1292036989514208</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.132540618048119</v>
+        <v>0.01179178280031044</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703478873271576</v>
+        <v>0.001703572925127941</v>
       </c>
       <c r="G2" t="n">
-        <v>1.782892248632804</v>
+        <v>2.35100665967826</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4577176679597431</v>
+        <v>-0.2548240989328883</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
